--- a/docs/gem5-fi/lsu/gem5-fi-LSU单元故障注入方案.xlsx
+++ b/docs/gem5-fi/lsu/gem5-fi-LSU单元故障注入方案.xlsx
@@ -10001,7 +10001,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <tabColor rgb="FF1F4E78"/>
   </sheetPr>
@@ -10220,25 +10220,47 @@
         <v>284</v>
       </c>
       <c r="P2" s="24"/>
-      <c r="Q2" s="24"/>
-      <c r="R2" s="24"/>
-      <c r="S2" s="24"/>
-      <c r="T2" s="24"/>
-      <c r="U2" s="24"/>
-      <c r="V2" s="24"/>
-      <c r="W2" s="24"/>
-      <c r="X2" s="36" t="str">
-        <f t="shared" ref="X2:X65" si="0">IF(OR(R2="",R2-AP2&lt;=0),"",AB2/(R2-AP2))</f>
-        <v/>
-      </c>
-      <c r="Y2" s="36" t="str">
-        <f t="shared" ref="Y2:Y65" si="1">IF(OR(Q2="",Q2=0),"",R2/Q2)</f>
-        <v/>
-      </c>
-      <c r="Z2" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA2" s="24"/>
+      <c r="Q2" t="n">
+        <v>30</v>
+      </c>
+      <c r="R2" t="n">
+        <v>30</v>
+      </c>
+      <c r="S2" t="n">
+        <v>13</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0%</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成(pilot-30)</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">旧波次 pilot（原载体 agu_addrmodes，gem5 b64c808d 平台；s0 实证 mode/preMode/lsuTier 与 RunID 一致）；17 例 simulator failure 单列</t>
+        </is>
+      </c>
       <c r="AB2" s="39"/>
       <c r="AC2" s="39"/>
       <c r="AD2" s="39"/>
@@ -10262,7 +10284,9 @@
         <v/>
       </c>
       <c r="AO2" s="43"/>
-      <c r="AP2" s="44"/>
+      <c r="AP2" t="n">
+        <v>17</v>
+      </c>
       <c r="AQ2" s="48" t="s">
         <v>1260</v>
       </c>
@@ -10314,25 +10338,47 @@
         <v>284</v>
       </c>
       <c r="P3" s="24"/>
-      <c r="Q3" s="24"/>
-      <c r="R3" s="24"/>
-      <c r="S3" s="24"/>
-      <c r="T3" s="24"/>
-      <c r="U3" s="24"/>
-      <c r="V3" s="24"/>
-      <c r="W3" s="24"/>
-      <c r="X3" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y3" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Z3" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA3" s="24"/>
+      <c r="Q3" t="n">
+        <v>30</v>
+      </c>
+      <c r="R3" t="n">
+        <v>30</v>
+      </c>
+      <c r="S3" t="n">
+        <v>17</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10.5%</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成(pilot-30)</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">旧波次 pilot（原载体 gap_bfs，gem5 b64c808d 平台；s0 实证 mode/preMode/lsuTier 与 RunID 一致）；11 例 simulator failure 单列</t>
+        </is>
+      </c>
       <c r="AB3" s="39"/>
       <c r="AC3" s="39"/>
       <c r="AD3" s="39"/>
@@ -10356,7 +10402,9 @@
         <v/>
       </c>
       <c r="AO3" s="45"/>
-      <c r="AP3" s="46"/>
+      <c r="AP3" t="n">
+        <v>11</v>
+      </c>
       <c r="AQ3" s="48" t="s">
         <v>1260</v>
       </c>
@@ -10408,25 +10456,47 @@
         <v>284</v>
       </c>
       <c r="P4" s="24"/>
-      <c r="Q4" s="24"/>
-      <c r="R4" s="24"/>
-      <c r="S4" s="24"/>
-      <c r="T4" s="24"/>
-      <c r="U4" s="24"/>
-      <c r="V4" s="24"/>
-      <c r="W4" s="24"/>
-      <c r="X4" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y4" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Z4" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA4" s="24"/>
+      <c r="Q4" t="n">
+        <v>30</v>
+      </c>
+      <c r="R4" t="n">
+        <v>30</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a(全simfail)</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成(pilot-30)</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">载体改指W1（D-2026-10-09-重跑，RunID/模型/频率不变）：原载体 agu_addrmodes（短流，eligible 531-265,016 低于所属档首发下限，F-047①）→ mibench/bin/w1_all（MiBench-TC23 十负载复合，census eligible addrpost/addrpre=1.39e9/1.38e9，F-052）；gem5 10590f62 平台（OBS/SEM 重建后）；分母 oracle = W1 golden（F-050 冻结）；30 例 simulator failure（SE page-table fault panic：故障地址越出映射区）单列，五类全零</t>
+        </is>
+      </c>
       <c r="AB4" s="39"/>
       <c r="AC4" s="39"/>
       <c r="AD4" s="39"/>
@@ -10450,7 +10520,9 @@
         <v/>
       </c>
       <c r="AO4" s="45"/>
-      <c r="AP4" s="46"/>
+      <c r="AP4" t="n">
+        <v>30</v>
+      </c>
       <c r="AQ4" s="48" t="s">
         <v>1260</v>
       </c>
@@ -10502,25 +10574,47 @@
         <v>284</v>
       </c>
       <c r="P5" s="24"/>
-      <c r="Q5" s="24"/>
-      <c r="R5" s="24"/>
-      <c r="S5" s="24"/>
-      <c r="T5" s="24"/>
-      <c r="U5" s="24"/>
-      <c r="V5" s="24"/>
-      <c r="W5" s="24"/>
-      <c r="X5" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y5" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Z5" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA5" s="24"/>
+      <c r="Q5" t="n">
+        <v>30</v>
+      </c>
+      <c r="R5" t="n">
+        <v>30</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a(全simfail)</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成(pilot-30)</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">载体改指W1（D-2026-10-09-重跑，RunID/模型/频率不变）：原载体 gap_bfs（短流，eligible 531-265,016 低于所属档首发下限，F-047①）→ mibench/bin/w1_all（MiBench-TC23 十负载复合，census eligible addrpost/addrpre=1.39e9/1.38e9，F-052）；gem5 10590f62 平台（OBS/SEM 重建后）；分母 oracle = W1 golden（F-050 冻结）；30 例 simulator failure（SE page-table fault panic：故障地址越出映射区）单列，五类全零</t>
+        </is>
+      </c>
       <c r="AB5" s="39"/>
       <c r="AC5" s="39"/>
       <c r="AD5" s="39"/>
@@ -10544,7 +10638,9 @@
         <v/>
       </c>
       <c r="AO5" s="45"/>
-      <c r="AP5" s="46"/>
+      <c r="AP5" t="n">
+        <v>30</v>
+      </c>
       <c r="AQ5" s="48" t="s">
         <v>1260</v>
       </c>
@@ -10596,25 +10692,47 @@
         <v>284</v>
       </c>
       <c r="P6" s="24"/>
-      <c r="Q6" s="24"/>
-      <c r="R6" s="24"/>
-      <c r="S6" s="24"/>
-      <c r="T6" s="24"/>
-      <c r="U6" s="24"/>
-      <c r="V6" s="24"/>
-      <c r="W6" s="24"/>
-      <c r="X6" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y6" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Z6" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA6" s="24"/>
+      <c r="Q6" t="n">
+        <v>30</v>
+      </c>
+      <c r="R6" t="n">
+        <v>30</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a(全simfail)</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成(pilot-30)</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">载体改指W1（D-2026-10-09-重跑，RunID/模型/频率不变）：原载体 agu_addrmodes（短流，eligible 531-265,016 低于所属档首发下限，F-047①）→ mibench/bin/w1_all（MiBench-TC23 十负载复合，census eligible addrpost/addrpre=1.39e9/1.38e9，F-052）；gem5 10590f62 平台（OBS/SEM 重建后）；分母 oracle = W1 golden（F-050 冻结）；30 例 simulator failure（SE page-table fault panic：故障地址越出映射区）单列，五类全零</t>
+        </is>
+      </c>
       <c r="AB6" s="39"/>
       <c r="AC6" s="39"/>
       <c r="AD6" s="39"/>
@@ -10638,7 +10756,9 @@
         <v/>
       </c>
       <c r="AO6" s="45"/>
-      <c r="AP6" s="46"/>
+      <c r="AP6" t="n">
+        <v>30</v>
+      </c>
       <c r="AQ6" s="48" t="s">
         <v>1260</v>
       </c>
@@ -10690,25 +10810,47 @@
         <v>284</v>
       </c>
       <c r="P7" s="24"/>
-      <c r="Q7" s="24"/>
-      <c r="R7" s="24"/>
-      <c r="S7" s="24"/>
-      <c r="T7" s="24"/>
-      <c r="U7" s="24"/>
-      <c r="V7" s="24"/>
-      <c r="W7" s="24"/>
-      <c r="X7" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y7" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Z7" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA7" s="24"/>
+      <c r="Q7" t="n">
+        <v>30</v>
+      </c>
+      <c r="R7" t="n">
+        <v>30</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25%</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成(pilot-30)</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">旧波次 pilot（原载体 gap_bfs，gem5 b64c808d 平台；s0 实证 mode/preMode/lsuTier 与 RunID 一致）；26 例 simulator failure 单列</t>
+        </is>
+      </c>
       <c r="AB7" s="39"/>
       <c r="AC7" s="39"/>
       <c r="AD7" s="39"/>
@@ -10732,7 +10874,9 @@
         <v/>
       </c>
       <c r="AO7" s="45"/>
-      <c r="AP7" s="46"/>
+      <c r="AP7" t="n">
+        <v>26</v>
+      </c>
       <c r="AQ7" s="48" t="s">
         <v>1260</v>
       </c>
@@ -10784,25 +10928,47 @@
         <v>305</v>
       </c>
       <c r="P8" s="24"/>
-      <c r="Q8" s="24"/>
-      <c r="R8" s="24"/>
-      <c r="S8" s="24"/>
-      <c r="T8" s="24"/>
-      <c r="U8" s="24"/>
-      <c r="V8" s="24"/>
-      <c r="W8" s="24"/>
-      <c r="X8" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y8" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Z8" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA8" s="24"/>
+      <c r="Q8" t="n">
+        <v>30</v>
+      </c>
+      <c r="R8" t="n">
+        <v>30</v>
+      </c>
+      <c r="S8" t="n">
+        <v>14</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12.5%</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成(pilot-30)</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">旧波次 pilot（原载体 agu_addrmodes，gem5 b64c808d 平台；s0 实证 mode/preMode/lsuTier 与 RunID 一致）；14 例 simulator failure 单列</t>
+        </is>
+      </c>
       <c r="AB8" s="39"/>
       <c r="AC8" s="39"/>
       <c r="AD8" s="39"/>
@@ -10826,7 +10992,9 @@
         <v/>
       </c>
       <c r="AO8" s="45"/>
-      <c r="AP8" s="46"/>
+      <c r="AP8" t="n">
+        <v>14</v>
+      </c>
       <c r="AQ8" s="48" t="s">
         <v>1265</v>
       </c>
@@ -10878,25 +11046,47 @@
         <v>305</v>
       </c>
       <c r="P9" s="24"/>
-      <c r="Q9" s="24"/>
-      <c r="R9" s="24"/>
-      <c r="S9" s="24"/>
-      <c r="T9" s="24"/>
-      <c r="U9" s="24"/>
-      <c r="V9" s="24"/>
-      <c r="W9" s="24"/>
-      <c r="X9" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y9" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Z9" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA9" s="24"/>
+      <c r="Q9" t="n">
+        <v>30</v>
+      </c>
+      <c r="R9" t="n">
+        <v>30</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25%</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成(pilot-30)</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">旧波次 pilot（原载体 gap_bfs，gem5 b64c808d 平台；s0 实证 mode/preMode/lsuTier 与 RunID 一致）；26 例 simulator failure 单列</t>
+        </is>
+      </c>
       <c r="AB9" s="39"/>
       <c r="AC9" s="39"/>
       <c r="AD9" s="39"/>
@@ -10920,7 +11110,9 @@
         <v/>
       </c>
       <c r="AO9" s="45"/>
-      <c r="AP9" s="46"/>
+      <c r="AP9" t="n">
+        <v>26</v>
+      </c>
       <c r="AQ9" s="48" t="s">
         <v>1265</v>
       </c>
@@ -10972,25 +11164,47 @@
         <v>305</v>
       </c>
       <c r="P10" s="24"/>
-      <c r="Q10" s="24"/>
-      <c r="R10" s="24"/>
-      <c r="S10" s="24"/>
-      <c r="T10" s="24"/>
-      <c r="U10" s="24"/>
-      <c r="V10" s="24"/>
-      <c r="W10" s="24"/>
-      <c r="X10" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y10" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Z10" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA10" s="24"/>
+      <c r="Q10" t="n">
+        <v>30</v>
+      </c>
+      <c r="R10" t="n">
+        <v>30</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a(全simfail)</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成(pilot-30)</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">载体改指W1（D-2026-10-09-重跑，RunID/模型/频率不变）：原载体 agu_addrmodes（短流，eligible 531-265,016 低于所属档首发下限，F-047①）→ mibench/bin/w1_all（MiBench-TC23 十负载复合，census eligible addrpost/addrpre=1.39e9/1.38e9，F-052）；gem5 10590f62 平台（OBS/SEM 重建后）；分母 oracle = W1 golden（F-050 冻结）；30 例 simulator failure（SE page-table fault panic：故障地址越出映射区）单列，五类全零</t>
+        </is>
+      </c>
       <c r="AB10" s="39"/>
       <c r="AC10" s="39"/>
       <c r="AD10" s="39"/>
@@ -11014,7 +11228,9 @@
         <v/>
       </c>
       <c r="AO10" s="45"/>
-      <c r="AP10" s="46"/>
+      <c r="AP10" t="n">
+        <v>30</v>
+      </c>
       <c r="AQ10" s="48" t="s">
         <v>1265</v>
       </c>
@@ -11066,25 +11282,47 @@
         <v>305</v>
       </c>
       <c r="P11" s="24"/>
-      <c r="Q11" s="24"/>
-      <c r="R11" s="24"/>
-      <c r="S11" s="24"/>
-      <c r="T11" s="24"/>
-      <c r="U11" s="24"/>
-      <c r="V11" s="24"/>
-      <c r="W11" s="24"/>
-      <c r="X11" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y11" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Z11" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA11" s="24"/>
+      <c r="Q11" t="n">
+        <v>33</v>
+      </c>
+      <c r="R11" t="n">
+        <v>33</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a(全simfail)</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成(pilot-30)</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">旧波次 pilot（原载体 gap_bfs，gem5 b64c808d 平台；s0 实证 mode/preMode/lsuTier 与 RunID 一致）；33 例 simulator failure 单列，五类全零</t>
+        </is>
+      </c>
       <c r="AB11" s="39"/>
       <c r="AC11" s="39"/>
       <c r="AD11" s="39"/>
@@ -11108,7 +11346,9 @@
         <v/>
       </c>
       <c r="AO11" s="45"/>
-      <c r="AP11" s="46"/>
+      <c r="AP11" t="n">
+        <v>33</v>
+      </c>
       <c r="AQ11" s="48" t="s">
         <v>1265</v>
       </c>
@@ -11175,10 +11415,16 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Z12" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA12" s="24"/>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已阻塞(注入器缺口)</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admission BLOCKED（P3 波次终态）：A03 stuck-at 模型未实现（清单执行规则 4）； Runs 未执行（0 attempted）；解除须补注入器实现 + Decision Request（清单执行规则 4，不得静默近似）</t>
+        </is>
+      </c>
       <c r="AB12" s="39"/>
       <c r="AC12" s="39"/>
       <c r="AD12" s="39"/>
@@ -11269,10 +11515,16 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Z13" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA13" s="24"/>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已阻塞(注入器缺口)</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admission BLOCKED（P3 波次终态）：A03 stuck-at 模型未实现（清单执行规则 4）； Runs 未执行（0 attempted）；解除须补注入器实现 + Decision Request（清单执行规则 4，不得静默近似）</t>
+        </is>
+      </c>
       <c r="AB13" s="39"/>
       <c r="AC13" s="39"/>
       <c r="AD13" s="39"/>
@@ -11348,25 +11600,47 @@
         <v>333</v>
       </c>
       <c r="P14" s="24"/>
-      <c r="Q14" s="24"/>
-      <c r="R14" s="24"/>
-      <c r="S14" s="24"/>
-      <c r="T14" s="24"/>
-      <c r="U14" s="24"/>
-      <c r="V14" s="24"/>
-      <c r="W14" s="24"/>
-      <c r="X14" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y14" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Z14" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA14" s="24"/>
+      <c r="Q14" t="n">
+        <v>33</v>
+      </c>
+      <c r="R14" t="n">
+        <v>33</v>
+      </c>
+      <c r="S14" t="n">
+        <v>21</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>5</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18.5%</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成(pilot-30)</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">旧波次 pilot（原载体 agu_addrmodes，gem5 b64c808d 平台；s0 实证 mode/preMode/lsuTier 与 RunID 一致）；6 例 simulator failure 单列</t>
+        </is>
+      </c>
       <c r="AB14" s="39"/>
       <c r="AC14" s="39"/>
       <c r="AD14" s="39"/>
@@ -11390,7 +11664,9 @@
         <v/>
       </c>
       <c r="AO14" s="45"/>
-      <c r="AP14" s="46"/>
+      <c r="AP14" t="n">
+        <v>6</v>
+      </c>
       <c r="AQ14" s="48" t="s">
         <v>1271</v>
       </c>
@@ -11442,25 +11718,47 @@
         <v>333</v>
       </c>
       <c r="P15" s="24"/>
-      <c r="Q15" s="24"/>
-      <c r="R15" s="24"/>
-      <c r="S15" s="24"/>
-      <c r="T15" s="24"/>
-      <c r="U15" s="24"/>
-      <c r="V15" s="24"/>
-      <c r="W15" s="24"/>
-      <c r="X15" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y15" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Z15" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA15" s="24"/>
+      <c r="Q15" t="n">
+        <v>33</v>
+      </c>
+      <c r="R15" t="n">
+        <v>33</v>
+      </c>
+      <c r="S15" t="n">
+        <v>22</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>8</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26.7%</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成(pilot-30)</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">旧波次 pilot（原载体 mini_check，gem5 b64c808d 平台；s0 实证 mode/preMode/lsuTier 与 RunID 一致）；3 例 simulator failure 单列</t>
+        </is>
+      </c>
       <c r="AB15" s="39"/>
       <c r="AC15" s="39"/>
       <c r="AD15" s="39"/>
@@ -11484,7 +11782,9 @@
         <v/>
       </c>
       <c r="AO15" s="45"/>
-      <c r="AP15" s="46"/>
+      <c r="AP15" t="n">
+        <v>3</v>
+      </c>
       <c r="AQ15" s="48" t="s">
         <v>1271</v>
       </c>
@@ -11536,25 +11836,47 @@
         <v>333</v>
       </c>
       <c r="P16" s="24"/>
-      <c r="Q16" s="24"/>
-      <c r="R16" s="24"/>
-      <c r="S16" s="24"/>
-      <c r="T16" s="24"/>
-      <c r="U16" s="24"/>
-      <c r="V16" s="24"/>
-      <c r="W16" s="24"/>
-      <c r="X16" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y16" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Z16" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA16" s="24"/>
+      <c r="Q16" t="n">
+        <v>30</v>
+      </c>
+      <c r="R16" t="n">
+        <v>30</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a(全simfail)</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成(pilot-30)</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">载体改指W1（D-2026-10-09-重跑，RunID/模型/频率不变）：原载体 agu_addrmodes（短流，eligible 531-265,016 低于所属档首发下限，F-047①）→ mibench/bin/w1_all（MiBench-TC23 十负载复合，census eligible addrpost/addrpre=1.39e9/1.38e9，F-052）；gem5 10590f62 平台（OBS/SEM 重建后）；分母 oracle = W1 golden（F-050 冻结）；30 例 simulator failure（SE page-table fault panic：故障地址越出映射区）单列，五类全零</t>
+        </is>
+      </c>
       <c r="AB16" s="39"/>
       <c r="AC16" s="39"/>
       <c r="AD16" s="39"/>
@@ -11578,7 +11900,9 @@
         <v/>
       </c>
       <c r="AO16" s="45"/>
-      <c r="AP16" s="46"/>
+      <c r="AP16" t="n">
+        <v>30</v>
+      </c>
       <c r="AQ16" s="48" t="s">
         <v>1271</v>
       </c>
@@ -11630,25 +11954,47 @@
         <v>333</v>
       </c>
       <c r="P17" s="24"/>
-      <c r="Q17" s="24"/>
-      <c r="R17" s="24"/>
-      <c r="S17" s="24"/>
-      <c r="T17" s="24"/>
-      <c r="U17" s="24"/>
-      <c r="V17" s="24"/>
-      <c r="W17" s="24"/>
-      <c r="X17" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y17" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Z17" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA17" s="24"/>
+      <c r="Q17" t="n">
+        <v>30</v>
+      </c>
+      <c r="R17" t="n">
+        <v>30</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a(全simfail)</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成(pilot-30)</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">载体改指W1（D-2026-10-09-重跑，RunID/模型/频率不变）：原载体 mini_check（短流，eligible 531-265,016 低于所属档首发下限，F-047①）→ mibench/bin/w1_all（MiBench-TC23 十负载复合，census eligible addrpost/addrpre=1.39e9/1.38e9，F-052）；gem5 10590f62 平台（OBS/SEM 重建后）；分母 oracle = W1 golden（F-050 冻结）；30 例 simulator failure（SE page-table fault panic：故障地址越出映射区）单列，五类全零</t>
+        </is>
+      </c>
       <c r="AB17" s="39"/>
       <c r="AC17" s="39"/>
       <c r="AD17" s="39"/>
@@ -11672,7 +12018,9 @@
         <v/>
       </c>
       <c r="AO17" s="45"/>
-      <c r="AP17" s="46"/>
+      <c r="AP17" t="n">
+        <v>30</v>
+      </c>
       <c r="AQ17" s="48" t="s">
         <v>1271</v>
       </c>
@@ -11724,25 +12072,47 @@
         <v>333</v>
       </c>
       <c r="P18" s="24"/>
-      <c r="Q18" s="24"/>
-      <c r="R18" s="24"/>
-      <c r="S18" s="24"/>
-      <c r="T18" s="24"/>
-      <c r="U18" s="24"/>
-      <c r="V18" s="24"/>
-      <c r="W18" s="24"/>
-      <c r="X18" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y18" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Z18" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA18" s="24"/>
+      <c r="Q18" t="n">
+        <v>33</v>
+      </c>
+      <c r="R18" t="n">
+        <v>33</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a(全simfail)</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成(pilot-30)</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">旧波次 pilot（原载体 agu_addrmodes，gem5 b64c808d 平台；s0 实证 mode/preMode/lsuTier 与 RunID 一致）；33 例 simulator failure 单列，五类全零</t>
+        </is>
+      </c>
       <c r="AB18" s="39"/>
       <c r="AC18" s="39"/>
       <c r="AD18" s="39"/>
@@ -11766,7 +12136,9 @@
         <v/>
       </c>
       <c r="AO18" s="45"/>
-      <c r="AP18" s="46"/>
+      <c r="AP18" t="n">
+        <v>33</v>
+      </c>
       <c r="AQ18" s="48" t="s">
         <v>1271</v>
       </c>
@@ -11818,25 +12190,47 @@
         <v>333</v>
       </c>
       <c r="P19" s="24"/>
-      <c r="Q19" s="24"/>
-      <c r="R19" s="24"/>
-      <c r="S19" s="24"/>
-      <c r="T19" s="24"/>
-      <c r="U19" s="24"/>
-      <c r="V19" s="24"/>
-      <c r="W19" s="24"/>
-      <c r="X19" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y19" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Z19" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA19" s="24"/>
+      <c r="Q19" t="n">
+        <v>33</v>
+      </c>
+      <c r="R19" t="n">
+        <v>33</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a(全simfail)</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成(pilot-30)</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">旧波次 pilot（原载体 mini_check，gem5 b64c808d 平台；s0 实证 mode/preMode/lsuTier 与 RunID 一致）；33 例 simulator failure 单列，五类全零</t>
+        </is>
+      </c>
       <c r="AB19" s="39"/>
       <c r="AC19" s="39"/>
       <c r="AD19" s="39"/>
@@ -11860,7 +12254,9 @@
         <v/>
       </c>
       <c r="AO19" s="45"/>
-      <c r="AP19" s="46"/>
+      <c r="AP19" t="n">
+        <v>33</v>
+      </c>
       <c r="AQ19" s="48" t="s">
         <v>1271</v>
       </c>
@@ -11912,25 +12308,47 @@
         <v>320</v>
       </c>
       <c r="P20" s="24"/>
-      <c r="Q20" s="24"/>
-      <c r="R20" s="24"/>
-      <c r="S20" s="24"/>
-      <c r="T20" s="24"/>
-      <c r="U20" s="24"/>
-      <c r="V20" s="24"/>
-      <c r="W20" s="24"/>
-      <c r="X20" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y20" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Z20" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA20" s="24"/>
+      <c r="Q20" t="n">
+        <v>33</v>
+      </c>
+      <c r="R20" t="n">
+        <v>31</v>
+      </c>
+      <c r="S20" t="n">
+        <v>21</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12.5%</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">93.9%</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成(pilot-30,数值待核对)</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">旧波次 pilot（原载体 agu_addrmodes，gem5 b64c808d 平台）；F-047 幻影修正（D-2026-10-10-Overlay 口径）：2 例无效样本剔除（Masked 23→21），激活 33→31 暂定——逐样本证据确认后方可转最终，raw_class 永久保留不覆盖；7 例 simulator failure 单列（保留原值）</t>
+        </is>
+      </c>
       <c r="AB20" s="39"/>
       <c r="AC20" s="39"/>
       <c r="AD20" s="39"/>
@@ -11954,7 +12372,9 @@
         <v/>
       </c>
       <c r="AO20" s="45"/>
-      <c r="AP20" s="46"/>
+      <c r="AP20" t="n">
+        <v>7</v>
+      </c>
       <c r="AQ20" s="48" t="s">
         <v>1275</v>
       </c>
@@ -12006,25 +12426,47 @@
         <v>320</v>
       </c>
       <c r="P21" s="24"/>
-      <c r="Q21" s="24"/>
-      <c r="R21" s="24"/>
-      <c r="S21" s="24"/>
-      <c r="T21" s="24"/>
-      <c r="U21" s="24"/>
-      <c r="V21" s="24"/>
-      <c r="W21" s="24"/>
-      <c r="X21" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y21" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Z21" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA21" s="24"/>
+      <c r="Q21" t="n">
+        <v>30</v>
+      </c>
+      <c r="R21" t="n">
+        <v>30</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0%</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成(pilot-30)</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">载体改指W1（D-2026-10-09-重跑，RunID/模型/频率不变）：原载体 agu_addrmodes（短流，eligible 531-265,016 低于所属档首发下限，F-047①）→ mibench/bin/w1_all（MiBench-TC23 十负载复合，census eligible addrpost/addrpre=1.39e9/1.38e9，F-052）；gem5 10590f62 平台（OBS/SEM 重建后）；分母 oracle = W1 golden（F-050 冻结）；1 例真实架构 Crash（guest_or_unknown，s22）+ 29 例 simulator failure 单列</t>
+        </is>
+      </c>
       <c r="AB21" s="39"/>
       <c r="AC21" s="39"/>
       <c r="AD21" s="39"/>
@@ -12048,7 +12490,9 @@
         <v/>
       </c>
       <c r="AO21" s="45"/>
-      <c r="AP21" s="46"/>
+      <c r="AP21" t="n">
+        <v>29</v>
+      </c>
       <c r="AQ21" s="48" t="s">
         <v>1275</v>
       </c>
@@ -12100,25 +12544,47 @@
         <v>320</v>
       </c>
       <c r="P22" s="24"/>
-      <c r="Q22" s="24"/>
-      <c r="R22" s="24"/>
-      <c r="S22" s="24"/>
-      <c r="T22" s="24"/>
-      <c r="U22" s="24"/>
-      <c r="V22" s="24"/>
-      <c r="W22" s="24"/>
-      <c r="X22" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y22" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Z22" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA22" s="24"/>
+      <c r="Q22" t="n">
+        <v>33</v>
+      </c>
+      <c r="R22" t="n">
+        <v>33</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a(全simfail)</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成(pilot-30)</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">旧波次 pilot（原载体 agu_addrmodes，gem5 b64c808d 平台；s0 实证 mode/preMode/lsuTier 与 RunID 一致）；33 例 simulator failure 单列，五类全零</t>
+        </is>
+      </c>
       <c r="AB22" s="39"/>
       <c r="AC22" s="39"/>
       <c r="AD22" s="39"/>
@@ -12142,7 +12608,9 @@
         <v/>
       </c>
       <c r="AO22" s="45"/>
-      <c r="AP22" s="46"/>
+      <c r="AP22" t="n">
+        <v>33</v>
+      </c>
       <c r="AQ22" s="48" t="s">
         <v>1275</v>
       </c>
@@ -12194,25 +12662,47 @@
         <v>333</v>
       </c>
       <c r="P23" s="24"/>
-      <c r="Q23" s="24"/>
-      <c r="R23" s="24"/>
-      <c r="S23" s="24"/>
-      <c r="T23" s="24"/>
-      <c r="U23" s="24"/>
-      <c r="V23" s="24"/>
-      <c r="W23" s="24"/>
-      <c r="X23" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y23" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Z23" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA23" s="24"/>
+      <c r="Q23" t="n">
+        <v>33</v>
+      </c>
+      <c r="R23" t="n">
+        <v>32</v>
+      </c>
+      <c r="S23" t="n">
+        <v>14</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.3%</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">97.0%</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成(pilot-30,数值待核对)</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">旧波次 pilot（原载体 agu_addrmodes，gem5 b64c808d 平台）；F-047 幻影修正（D-2026-10-10-Overlay 口径）：1 例无效样本剔除（Masked 15→14），激活 33→32 暂定——逐样本证据确认后方可转最终，raw_class 永久保留不覆盖；16 例 simulator failure 单列（保留原值）</t>
+        </is>
+      </c>
       <c r="AB23" s="39"/>
       <c r="AC23" s="39"/>
       <c r="AD23" s="39"/>
@@ -12236,7 +12726,9 @@
         <v/>
       </c>
       <c r="AO23" s="45"/>
-      <c r="AP23" s="46"/>
+      <c r="AP23" t="n">
+        <v>16</v>
+      </c>
       <c r="AQ23" s="48" t="s">
         <v>1277</v>
       </c>
@@ -12288,25 +12780,47 @@
         <v>333</v>
       </c>
       <c r="P24" s="24"/>
-      <c r="Q24" s="24"/>
-      <c r="R24" s="24"/>
-      <c r="S24" s="24"/>
-      <c r="T24" s="24"/>
-      <c r="U24" s="24"/>
-      <c r="V24" s="24"/>
-      <c r="W24" s="24"/>
-      <c r="X24" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y24" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Z24" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA24" s="24"/>
+      <c r="Q24" t="n">
+        <v>33</v>
+      </c>
+      <c r="R24" t="n">
+        <v>33</v>
+      </c>
+      <c r="S24" t="n">
+        <v>19</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0%</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成(pilot-30)</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">旧波次 pilot（原载体 sq_forward，gem5 b64c808d 平台；s0 实证 mode/preMode/lsuTier 与 RunID 一致）；14 例 simulator failure 单列</t>
+        </is>
+      </c>
       <c r="AB24" s="39"/>
       <c r="AC24" s="39"/>
       <c r="AD24" s="39"/>
@@ -12330,7 +12844,9 @@
         <v/>
       </c>
       <c r="AO24" s="45"/>
-      <c r="AP24" s="46"/>
+      <c r="AP24" t="n">
+        <v>14</v>
+      </c>
       <c r="AQ24" s="48" t="s">
         <v>1277</v>
       </c>
@@ -12382,25 +12898,47 @@
         <v>333</v>
       </c>
       <c r="P25" s="24"/>
-      <c r="Q25" s="24"/>
-      <c r="R25" s="24"/>
-      <c r="S25" s="24"/>
-      <c r="T25" s="24"/>
-      <c r="U25" s="24"/>
-      <c r="V25" s="24"/>
-      <c r="W25" s="24"/>
-      <c r="X25" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y25" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Z25" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA25" s="24"/>
+      <c r="Q25" t="n">
+        <v>30</v>
+      </c>
+      <c r="R25" t="n">
+        <v>30</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a(全simfail)</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成(pilot-30)</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">载体改指W1（D-2026-10-09-重跑，RunID/模型/频率不变）：原载体 agu_addrmodes（短流，eligible 531-265,016 低于所属档首发下限，F-047①）→ mibench/bin/w1_all（MiBench-TC23 十负载复合，census eligible addrpost/addrpre=1.39e9/1.38e9，F-052）；gem5 10590f62 平台（OBS/SEM 重建后）；分母 oracle = W1 golden（F-050 冻结）；30 例 simulator failure（SE page-table fault panic：故障地址越出映射区）单列，五类全零</t>
+        </is>
+      </c>
       <c r="AB25" s="39"/>
       <c r="AC25" s="39"/>
       <c r="AD25" s="39"/>
@@ -12424,7 +12962,9 @@
         <v/>
       </c>
       <c r="AO25" s="45"/>
-      <c r="AP25" s="46"/>
+      <c r="AP25" t="n">
+        <v>30</v>
+      </c>
       <c r="AQ25" s="48" t="s">
         <v>1277</v>
       </c>
@@ -12476,25 +13016,47 @@
         <v>333</v>
       </c>
       <c r="P26" s="24"/>
-      <c r="Q26" s="24"/>
-      <c r="R26" s="24"/>
-      <c r="S26" s="24"/>
-      <c r="T26" s="24"/>
-      <c r="U26" s="24"/>
-      <c r="V26" s="24"/>
-      <c r="W26" s="24"/>
-      <c r="X26" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y26" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Z26" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA26" s="24"/>
+      <c r="Q26" t="n">
+        <v>30</v>
+      </c>
+      <c r="R26" t="n">
+        <v>30</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a(全simfail)</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成(pilot-30)</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">载体改指W1（D-2026-10-09-重跑，RunID/模型/频率不变）：原载体 sq_forward（短流，eligible 531-265,016 低于所属档首发下限，F-047①）→ mibench/bin/w1_all（MiBench-TC23 十负载复合，census eligible addrpost/addrpre=1.39e9/1.38e9，F-052）；gem5 10590f62 平台（OBS/SEM 重建后）；分母 oracle = W1 golden（F-050 冻结）；30 例 simulator failure（SE page-table fault panic：故障地址越出映射区）单列，五类全零</t>
+        </is>
+      </c>
       <c r="AB26" s="39"/>
       <c r="AC26" s="39"/>
       <c r="AD26" s="39"/>
@@ -12518,7 +13080,9 @@
         <v/>
       </c>
       <c r="AO26" s="45"/>
-      <c r="AP26" s="46"/>
+      <c r="AP26" t="n">
+        <v>30</v>
+      </c>
       <c r="AQ26" s="48" t="s">
         <v>1277</v>
       </c>
@@ -12570,25 +13134,47 @@
         <v>333</v>
       </c>
       <c r="P27" s="24"/>
-      <c r="Q27" s="24"/>
-      <c r="R27" s="24"/>
-      <c r="S27" s="24"/>
-      <c r="T27" s="24"/>
-      <c r="U27" s="24"/>
-      <c r="V27" s="24"/>
-      <c r="W27" s="24"/>
-      <c r="X27" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y27" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Z27" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA27" s="24"/>
+      <c r="Q27" t="n">
+        <v>33</v>
+      </c>
+      <c r="R27" t="n">
+        <v>33</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a(全simfail)</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成(pilot-30)</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">旧波次 pilot（原载体 agu_addrmodes，gem5 b64c808d 平台；s0 实证 mode/preMode/lsuTier 与 RunID 一致）；33 例 simulator failure 单列，五类全零</t>
+        </is>
+      </c>
       <c r="AB27" s="39"/>
       <c r="AC27" s="39"/>
       <c r="AD27" s="39"/>
@@ -12612,7 +13198,9 @@
         <v/>
       </c>
       <c r="AO27" s="45"/>
-      <c r="AP27" s="46"/>
+      <c r="AP27" t="n">
+        <v>33</v>
+      </c>
       <c r="AQ27" s="48" t="s">
         <v>1277</v>
       </c>
@@ -12664,25 +13252,47 @@
         <v>333</v>
       </c>
       <c r="P28" s="24"/>
-      <c r="Q28" s="24"/>
-      <c r="R28" s="24"/>
-      <c r="S28" s="24"/>
-      <c r="T28" s="24"/>
-      <c r="U28" s="24"/>
-      <c r="V28" s="24"/>
-      <c r="W28" s="24"/>
-      <c r="X28" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y28" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Z28" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA28" s="24"/>
+      <c r="Q28" t="n">
+        <v>33</v>
+      </c>
+      <c r="R28" t="n">
+        <v>33</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a(全simfail)</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成(pilot-30)</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">旧波次 pilot（原载体 sq_forward，gem5 b64c808d 平台；s0 实证 mode/preMode/lsuTier 与 RunID 一致）；33 例 simulator failure 单列，五类全零</t>
+        </is>
+      </c>
       <c r="AB28" s="39"/>
       <c r="AC28" s="39"/>
       <c r="AD28" s="39"/>
@@ -12706,7 +13316,9 @@
         <v/>
       </c>
       <c r="AO28" s="45"/>
-      <c r="AP28" s="46"/>
+      <c r="AP28" t="n">
+        <v>33</v>
+      </c>
       <c r="AQ28" s="48" t="s">
         <v>1277</v>
       </c>
@@ -12773,10 +13385,16 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Z29" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA29" s="24"/>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已阻塞(注入器缺口)</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admission BLOCKED（P3 波次终态）：A07 全系列注入器缺口（MODEL_BLOCKED，F-047 审计确认）； Runs 未执行（0 attempted）；解除须补注入器实现 + Decision Request（清单执行规则 4，不得静默近似）</t>
+        </is>
+      </c>
       <c r="AB29" s="39"/>
       <c r="AC29" s="39"/>
       <c r="AD29" s="39"/>
@@ -12867,10 +13485,16 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Z30" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA30" s="24"/>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已阻塞(注入器缺口)</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admission BLOCKED（P3 波次终态）：A07 全系列注入器缺口（MODEL_BLOCKED，F-047 审计确认）； Runs 未执行（0 attempted）；解除须补注入器实现 + Decision Request（清单执行规则 4，不得静默近似）</t>
+        </is>
+      </c>
       <c r="AB30" s="39"/>
       <c r="AC30" s="39"/>
       <c r="AD30" s="39"/>
@@ -12961,10 +13585,16 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Z31" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA31" s="24"/>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已阻塞(注入器缺口)</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admission BLOCKED（P3 波次终态）：A07 全系列注入器缺口（MODEL_BLOCKED，F-047 审计确认）； Runs 未执行（0 attempted）；解除须补注入器实现 + Decision Request（清单执行规则 4，不得静默近似）</t>
+        </is>
+      </c>
       <c r="AB31" s="39"/>
       <c r="AC31" s="39"/>
       <c r="AD31" s="39"/>
@@ -13055,10 +13685,16 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Z32" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA32" s="24"/>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已阻塞(注入器缺口)</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admission BLOCKED（P3 波次终态）：A07 全系列注入器缺口（MODEL_BLOCKED，F-047 审计确认）； Runs 未执行（0 attempted）；解除须补注入器实现 + Decision Request（清单执行规则 4，不得静默近似）</t>
+        </is>
+      </c>
       <c r="AB32" s="39"/>
       <c r="AC32" s="39"/>
       <c r="AD32" s="39"/>
@@ -13149,10 +13785,16 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Z33" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA33" s="24"/>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已阻塞(注入器缺口)</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admission BLOCKED（P3 波次终态）：A07 全系列注入器缺口（MODEL_BLOCKED，F-047 审计确认）； Runs 未执行（0 attempted）；解除须补注入器实现 + Decision Request（清单执行规则 4，不得静默近似）</t>
+        </is>
+      </c>
       <c r="AB33" s="39"/>
       <c r="AC33" s="39"/>
       <c r="AD33" s="39"/>
@@ -13243,10 +13885,16 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Z34" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA34" s="24"/>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已阻塞(注入器缺口)</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admission BLOCKED（P3 波次终态）：A07 全系列注入器缺口（MODEL_BLOCKED，F-047 审计确认）； Runs 未执行（0 attempted）；解除须补注入器实现 + Decision Request（清单执行规则 4，不得静默近似）</t>
+        </is>
+      </c>
       <c r="AB34" s="39"/>
       <c r="AC34" s="39"/>
       <c r="AD34" s="39"/>
@@ -13322,25 +13970,47 @@
         <v>320</v>
       </c>
       <c r="P35" s="24"/>
-      <c r="Q35" s="24"/>
-      <c r="R35" s="24"/>
-      <c r="S35" s="24"/>
-      <c r="T35" s="24"/>
-      <c r="U35" s="24"/>
-      <c r="V35" s="24"/>
-      <c r="W35" s="24"/>
-      <c r="X35" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y35" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Z35" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA35" s="24"/>
+      <c r="Q35" t="n">
+        <v>33</v>
+      </c>
+      <c r="R35" t="n">
+        <v>33</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10.7%</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成(pilot-30)</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">旧波次 pilot（原载体 agu_addrmodes，gem5 b64c808d 平台；s0 实证 mode/preMode/lsuTier 与 RunID 一致）；5 例 simulator failure 单列</t>
+        </is>
+      </c>
       <c r="AB35" s="39"/>
       <c r="AC35" s="39"/>
       <c r="AD35" s="39"/>
@@ -13364,7 +14034,9 @@
         <v/>
       </c>
       <c r="AO35" s="45"/>
-      <c r="AP35" s="46"/>
+      <c r="AP35" t="n">
+        <v>5</v>
+      </c>
       <c r="AQ35" s="48" t="s">
         <v>1283</v>
       </c>
@@ -13416,25 +14088,47 @@
         <v>320</v>
       </c>
       <c r="P36" s="24"/>
-      <c r="Q36" s="24"/>
-      <c r="R36" s="24"/>
-      <c r="S36" s="24"/>
-      <c r="T36" s="24"/>
-      <c r="U36" s="24"/>
-      <c r="V36" s="24"/>
-      <c r="W36" s="24"/>
-      <c r="X36" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y36" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Z36" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA36" s="24"/>
+      <c r="Q36" t="n">
+        <v>33</v>
+      </c>
+      <c r="R36" t="n">
+        <v>33</v>
+      </c>
+      <c r="S36" t="n">
+        <v>27</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0%</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成(pilot-30)</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">旧波次 pilot（原载体 sq_forward，gem5 b64c808d 平台；s0 实证 mode/preMode/lsuTier 与 RunID 一致）；6 例 simulator failure 单列</t>
+        </is>
+      </c>
       <c r="AB36" s="39"/>
       <c r="AC36" s="39"/>
       <c r="AD36" s="39"/>
@@ -13458,7 +14152,9 @@
         <v/>
       </c>
       <c r="AO36" s="45"/>
-      <c r="AP36" s="46"/>
+      <c r="AP36" t="n">
+        <v>6</v>
+      </c>
       <c r="AQ36" s="48" t="s">
         <v>1283</v>
       </c>
@@ -13510,25 +14206,47 @@
         <v>320</v>
       </c>
       <c r="P37" s="24"/>
-      <c r="Q37" s="24"/>
-      <c r="R37" s="24"/>
-      <c r="S37" s="24"/>
-      <c r="T37" s="24"/>
-      <c r="U37" s="24"/>
-      <c r="V37" s="24"/>
-      <c r="W37" s="24"/>
-      <c r="X37" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y37" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Z37" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA37" s="24"/>
+      <c r="Q37" t="n">
+        <v>30</v>
+      </c>
+      <c r="R37" t="n">
+        <v>30</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a(全simfail)</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成(pilot-30)</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">载体改指W1（D-2026-10-09-重跑，RunID/模型/频率不变）：原载体 agu_addrmodes（短流，eligible 531-265,016 低于所属档首发下限，F-047①）→ mibench/bin/w1_all（MiBench-TC23 十负载复合，census eligible addrpost/addrpre=1.39e9/1.38e9，F-052）；gem5 10590f62 平台（OBS/SEM 重建后）；分母 oracle = W1 golden（F-050 冻结）；30 例 simulator failure（SE page-table fault panic：故障地址越出映射区）单列，五类全零</t>
+        </is>
+      </c>
       <c r="AB37" s="39"/>
       <c r="AC37" s="39"/>
       <c r="AD37" s="39"/>
@@ -13552,7 +14270,9 @@
         <v/>
       </c>
       <c r="AO37" s="45"/>
-      <c r="AP37" s="46"/>
+      <c r="AP37" t="n">
+        <v>30</v>
+      </c>
       <c r="AQ37" s="48" t="s">
         <v>1283</v>
       </c>
@@ -13604,25 +14324,47 @@
         <v>320</v>
       </c>
       <c r="P38" s="24"/>
-      <c r="Q38" s="24"/>
-      <c r="R38" s="24"/>
-      <c r="S38" s="24"/>
-      <c r="T38" s="24"/>
-      <c r="U38" s="24"/>
-      <c r="V38" s="24"/>
-      <c r="W38" s="24"/>
-      <c r="X38" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y38" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Z38" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA38" s="24"/>
+      <c r="Q38" t="n">
+        <v>30</v>
+      </c>
+      <c r="R38" t="n">
+        <v>30</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a(全simfail)</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成(pilot-30)</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">载体改指W1（D-2026-10-09-重跑，RunID/模型/频率不变）：原载体 sq_forward（短流，eligible 531-265,016 低于所属档首发下限，F-047①）→ mibench/bin/w1_all（MiBench-TC23 十负载复合，census eligible addrpost/addrpre=1.39e9/1.38e9，F-052）；gem5 10590f62 平台（OBS/SEM 重建后）；分母 oracle = W1 golden（F-050 冻结）；30 例 simulator failure（SE page-table fault panic：故障地址越出映射区）单列，五类全零</t>
+        </is>
+      </c>
       <c r="AB38" s="39"/>
       <c r="AC38" s="39"/>
       <c r="AD38" s="39"/>
@@ -13646,7 +14388,9 @@
         <v/>
       </c>
       <c r="AO38" s="45"/>
-      <c r="AP38" s="46"/>
+      <c r="AP38" t="n">
+        <v>30</v>
+      </c>
       <c r="AQ38" s="48" t="s">
         <v>1283</v>
       </c>
@@ -13698,25 +14442,47 @@
         <v>320</v>
       </c>
       <c r="P39" s="24"/>
-      <c r="Q39" s="24"/>
-      <c r="R39" s="24"/>
-      <c r="S39" s="24"/>
-      <c r="T39" s="24"/>
-      <c r="U39" s="24"/>
-      <c r="V39" s="24"/>
-      <c r="W39" s="24"/>
-      <c r="X39" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y39" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Z39" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA39" s="24"/>
+      <c r="Q39" t="n">
+        <v>33</v>
+      </c>
+      <c r="R39" t="n">
+        <v>33</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a(全simfail)</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成(pilot-30)</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">旧波次 pilot（原载体 agu_addrmodes，gem5 b64c808d 平台；s0 实证 mode/preMode/lsuTier 与 RunID 一致）；33 例 simulator failure 单列，五类全零</t>
+        </is>
+      </c>
       <c r="AB39" s="39"/>
       <c r="AC39" s="39"/>
       <c r="AD39" s="39"/>
@@ -13740,7 +14506,9 @@
         <v/>
       </c>
       <c r="AO39" s="45"/>
-      <c r="AP39" s="46"/>
+      <c r="AP39" t="n">
+        <v>33</v>
+      </c>
       <c r="AQ39" s="48" t="s">
         <v>1283</v>
       </c>
@@ -13792,25 +14560,47 @@
         <v>320</v>
       </c>
       <c r="P40" s="24"/>
-      <c r="Q40" s="24"/>
-      <c r="R40" s="24"/>
-      <c r="S40" s="24"/>
-      <c r="T40" s="24"/>
-      <c r="U40" s="24"/>
-      <c r="V40" s="24"/>
-      <c r="W40" s="24"/>
-      <c r="X40" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y40" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Z40" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA40" s="24"/>
+      <c r="Q40" t="n">
+        <v>33</v>
+      </c>
+      <c r="R40" t="n">
+        <v>33</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a(全simfail)</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成(pilot-30)</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">旧波次 pilot（原载体 sq_forward，gem5 b64c808d 平台；s0 实证 mode/preMode/lsuTier 与 RunID 一致）；33 例 simulator failure 单列，五类全零</t>
+        </is>
+      </c>
       <c r="AB40" s="39"/>
       <c r="AC40" s="39"/>
       <c r="AD40" s="39"/>
@@ -13834,7 +14624,9 @@
         <v/>
       </c>
       <c r="AO40" s="45"/>
-      <c r="AP40" s="46"/>
+      <c r="AP40" t="n">
+        <v>33</v>
+      </c>
       <c r="AQ40" s="48" t="s">
         <v>1283</v>
       </c>
@@ -35600,25 +36392,47 @@
         <v>1018</v>
       </c>
       <c r="P272" s="34"/>
-      <c r="Q272" s="34"/>
-      <c r="R272" s="34"/>
-      <c r="S272" s="34"/>
-      <c r="T272" s="34"/>
-      <c r="U272" s="34"/>
-      <c r="V272" s="34"/>
-      <c r="W272" s="34"/>
-      <c r="X272" s="37" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="Y272" s="37" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="Z272" s="35" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA272" s="34"/>
+      <c r="Q272" t="n">
+        <v>30</v>
+      </c>
+      <c r="R272" t="n">
+        <v>16</v>
+      </c>
+      <c r="S272" t="n">
+        <v>9</v>
+      </c>
+      <c r="T272" t="n">
+        <v>0</v>
+      </c>
+      <c r="U272" t="n">
+        <v>0</v>
+      </c>
+      <c r="V272" t="n">
+        <v>0</v>
+      </c>
+      <c r="W272" t="n">
+        <v>0</v>
+      </c>
+      <c r="X272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0%</t>
+        </is>
+      </c>
+      <c r="Y272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">53.3%</t>
+        </is>
+      </c>
+      <c r="Z272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成(pilot-30,数值待核对)</t>
+        </is>
+      </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">旧波次 pilot（原载体 sq_forward，gem5 b64c808d 平台）；F-047 幻影修正（D-2026-10-10-Overlay 口径）：14 例无效样本剔除（Masked 23→9），激活 30→16 暂定——逐样本证据确认后方可转最终，raw_class 永久保留不覆盖；7 例 simulator failure 单列（保留原值）</t>
+        </is>
+      </c>
       <c r="AB272" s="39"/>
       <c r="AC272" s="39"/>
       <c r="AD272" s="39"/>
@@ -35642,7 +36456,9 @@
         <v/>
       </c>
       <c r="AO272" s="45"/>
-      <c r="AP272" s="46"/>
+      <c r="AP272" t="n">
+        <v>7</v>
+      </c>
       <c r="AQ272" s="48" t="s">
         <v>1320</v>
       </c>
@@ -35882,25 +36698,47 @@
         <v>1018</v>
       </c>
       <c r="P275" s="34"/>
-      <c r="Q275" s="34"/>
-      <c r="R275" s="34"/>
-      <c r="S275" s="34"/>
-      <c r="T275" s="34"/>
-      <c r="U275" s="34"/>
-      <c r="V275" s="34"/>
-      <c r="W275" s="34"/>
-      <c r="X275" s="37" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="Y275" s="37" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="Z275" s="35" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA275" s="34"/>
+      <c r="Q275" t="n">
+        <v>30</v>
+      </c>
+      <c r="R275" t="n">
+        <v>30</v>
+      </c>
+      <c r="S275" t="n">
+        <v>0</v>
+      </c>
+      <c r="T275" t="n">
+        <v>0</v>
+      </c>
+      <c r="U275" t="n">
+        <v>0</v>
+      </c>
+      <c r="V275" t="n">
+        <v>0</v>
+      </c>
+      <c r="W275" t="n">
+        <v>0</v>
+      </c>
+      <c r="X275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a(全simfail)</t>
+        </is>
+      </c>
+      <c r="Y275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="Z275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成(pilot-30)</t>
+        </is>
+      </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">载体改指W1（D-2026-10-09-重跑，RunID/模型/频率不变）：原载体 sq_forward（短流，eligible 531-265,016 低于所属档首发下限，F-047①）→ mibench/bin/w1_all（MiBench-TC23 十负载复合，census eligible addrpost/addrpre=1.39e9/1.38e9，F-052）；gem5 10590f62 平台（OBS/SEM 重建后）；分母 oracle = W1 golden（F-050 冻结）；30 例 simulator failure（SE page-table fault panic：故障地址越出映射区）单列，五类全零</t>
+        </is>
+      </c>
       <c r="AB275" s="39"/>
       <c r="AC275" s="39"/>
       <c r="AD275" s="39"/>
@@ -35924,7 +36762,9 @@
         <v/>
       </c>
       <c r="AO275" s="45"/>
-      <c r="AP275" s="46"/>
+      <c r="AP275" t="n">
+        <v>30</v>
+      </c>
       <c r="AQ275" s="48" t="s">
         <v>1320</v>
       </c>
@@ -36164,25 +37004,47 @@
         <v>1018</v>
       </c>
       <c r="P278" s="34"/>
-      <c r="Q278" s="34"/>
-      <c r="R278" s="34"/>
-      <c r="S278" s="34"/>
-      <c r="T278" s="34"/>
-      <c r="U278" s="34"/>
-      <c r="V278" s="34"/>
-      <c r="W278" s="34"/>
-      <c r="X278" s="37" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="Y278" s="37" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="Z278" s="35" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA278" s="34"/>
+      <c r="Q278" t="n">
+        <v>30</v>
+      </c>
+      <c r="R278" t="n">
+        <v>30</v>
+      </c>
+      <c r="S278" t="n">
+        <v>0</v>
+      </c>
+      <c r="T278" t="n">
+        <v>0</v>
+      </c>
+      <c r="U278" t="n">
+        <v>0</v>
+      </c>
+      <c r="V278" t="n">
+        <v>0</v>
+      </c>
+      <c r="W278" t="n">
+        <v>0</v>
+      </c>
+      <c r="X278" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a(全simfail)</t>
+        </is>
+      </c>
+      <c r="Y278" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="Z278" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成(pilot-30)</t>
+        </is>
+      </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t xml:space="preserve">载体改指W1（D-2026-10-09-重跑，RunID/模型/频率不变）：原载体 sq_forward（短流，eligible 531-265,016 低于所属档首发下限，F-047①）→ mibench/bin/w1_all（MiBench-TC23 十负载复合，census eligible addrpost/addrpre=1.39e9/1.38e9，F-052）；gem5 10590f62 平台（OBS/SEM 重建后）；分母 oracle = W1 golden（F-050 冻结）；30 例 simulator failure（SE page-table fault panic：故障地址越出映射区）单列，五类全零</t>
+        </is>
+      </c>
       <c r="AB278" s="39"/>
       <c r="AC278" s="39"/>
       <c r="AD278" s="39"/>
@@ -36206,7 +37068,9 @@
         <v/>
       </c>
       <c r="AO278" s="45"/>
-      <c r="AP278" s="46"/>
+      <c r="AP278" t="n">
+        <v>30</v>
+      </c>
       <c r="AQ278" s="48" t="s">
         <v>1320</v>
       </c>
@@ -36352,25 +37216,47 @@
         <v>1035</v>
       </c>
       <c r="P280" s="34"/>
-      <c r="Q280" s="34"/>
-      <c r="R280" s="34"/>
-      <c r="S280" s="34"/>
-      <c r="T280" s="34"/>
-      <c r="U280" s="34"/>
-      <c r="V280" s="34"/>
-      <c r="W280" s="34"/>
-      <c r="X280" s="37" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="Y280" s="37" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="Z280" s="35" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA280" s="34"/>
+      <c r="Q280" t="n">
+        <v>33</v>
+      </c>
+      <c r="R280" t="n">
+        <v>19</v>
+      </c>
+      <c r="S280" t="n">
+        <v>19</v>
+      </c>
+      <c r="T280" t="n">
+        <v>0</v>
+      </c>
+      <c r="U280" t="n">
+        <v>0</v>
+      </c>
+      <c r="V280" t="n">
+        <v>0</v>
+      </c>
+      <c r="W280" t="n">
+        <v>0</v>
+      </c>
+      <c r="X280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0%</t>
+        </is>
+      </c>
+      <c r="Y280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57.6%</t>
+        </is>
+      </c>
+      <c r="Z280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成(pilot-30,数值待核对)</t>
+        </is>
+      </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">旧波次 pilot（原载体 sq_forward，gem5 b64c808d 平台）；F-047 幻影修正（D-2026-10-10-Overlay 口径）：14 例无效样本剔除（Masked 33→19），激活 33→19 暂定——逐样本证据确认后方可转最终，raw_class 永久保留不覆盖</t>
+        </is>
+      </c>
       <c r="AB280" s="39"/>
       <c r="AC280" s="39"/>
       <c r="AD280" s="39"/>
@@ -36394,7 +37280,9 @@
         <v/>
       </c>
       <c r="AO280" s="45"/>
-      <c r="AP280" s="46"/>
+      <c r="AP280" t="n">
+        <v>0</v>
+      </c>
       <c r="AQ280" s="48" t="s">
         <v>1323</v>
       </c>
@@ -36540,25 +37428,47 @@
         <v>1035</v>
       </c>
       <c r="P282" s="34"/>
-      <c r="Q282" s="34"/>
-      <c r="R282" s="34"/>
-      <c r="S282" s="34"/>
-      <c r="T282" s="34"/>
-      <c r="U282" s="34"/>
-      <c r="V282" s="34"/>
-      <c r="W282" s="34"/>
-      <c r="X282" s="37" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="Y282" s="37" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="Z282" s="35" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA282" s="34"/>
+      <c r="Q282" t="n">
+        <v>30</v>
+      </c>
+      <c r="R282" t="n">
+        <v>30</v>
+      </c>
+      <c r="S282" t="n">
+        <v>0</v>
+      </c>
+      <c r="T282" t="n">
+        <v>0</v>
+      </c>
+      <c r="U282" t="n">
+        <v>0</v>
+      </c>
+      <c r="V282" t="n">
+        <v>0</v>
+      </c>
+      <c r="W282" t="n">
+        <v>0</v>
+      </c>
+      <c r="X282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a(全simfail)</t>
+        </is>
+      </c>
+      <c r="Y282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="Z282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成(pilot-30)</t>
+        </is>
+      </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">载体改指W1（D-2026-10-09-重跑，RunID/模型/频率不变）：原载体 sq_forward（短流，eligible 531-265,016 低于所属档首发下限，F-047①）→ mibench/bin/w1_all（MiBench-TC23 十负载复合，census eligible addrpost/addrpre=1.39e9/1.38e9，F-052）；gem5 10590f62 平台（OBS/SEM 重建后）；分母 oracle = W1 golden（F-050 冻结）；30 例 simulator failure（SE page-table fault panic：故障地址越出映射区）单列，五类全零</t>
+        </is>
+      </c>
       <c r="AB282" s="39"/>
       <c r="AC282" s="39"/>
       <c r="AD282" s="39"/>
@@ -36582,7 +37492,9 @@
         <v/>
       </c>
       <c r="AO282" s="45"/>
-      <c r="AP282" s="46"/>
+      <c r="AP282" t="n">
+        <v>30</v>
+      </c>
       <c r="AQ282" s="48" t="s">
         <v>1323</v>
       </c>
@@ -36728,25 +37640,47 @@
         <v>1035</v>
       </c>
       <c r="P284" s="34"/>
-      <c r="Q284" s="34"/>
-      <c r="R284" s="34"/>
-      <c r="S284" s="34"/>
-      <c r="T284" s="34"/>
-      <c r="U284" s="34"/>
-      <c r="V284" s="34"/>
-      <c r="W284" s="34"/>
-      <c r="X284" s="37" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="Y284" s="37" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="Z284" s="35" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA284" s="34"/>
+      <c r="Q284" t="n">
+        <v>33</v>
+      </c>
+      <c r="R284" t="n">
+        <v>33</v>
+      </c>
+      <c r="S284" t="n">
+        <v>33</v>
+      </c>
+      <c r="T284" t="n">
+        <v>0</v>
+      </c>
+      <c r="U284" t="n">
+        <v>0</v>
+      </c>
+      <c r="V284" t="n">
+        <v>0</v>
+      </c>
+      <c r="W284" t="n">
+        <v>0</v>
+      </c>
+      <c r="X284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0%</t>
+        </is>
+      </c>
+      <c r="Y284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="Z284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成(pilot-30)</t>
+        </is>
+      </c>
+      <c r="AA284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">旧波次 pilot（原载体 sq_forward，gem5 b64c808d 平台；s0 实证 mode/preMode/lsuTier 与 RunID 一致）</t>
+        </is>
+      </c>
       <c r="AB284" s="39"/>
       <c r="AC284" s="39"/>
       <c r="AD284" s="39"/>
@@ -36770,7 +37704,9 @@
         <v/>
       </c>
       <c r="AO284" s="45"/>
-      <c r="AP284" s="46"/>
+      <c r="AP284" t="n">
+        <v>0</v>
+      </c>
       <c r="AQ284" s="48" t="s">
         <v>1323</v>
       </c>
@@ -36931,10 +37867,16 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="Z286" s="35" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA286" s="34"/>
+      <c r="Z286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已阻塞(模型身份失真,待重跑)</t>
+        </is>
+      </c>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">模型身份失真（D-2026-10-10-ITEM285撤销）：--lsqfwd_l03 参数 argparse 收下但 lsu_proxy.py 挂载块不传、CHAOSLSQFwd 无此 Param，s0 config.ini 实证实际执行 structMode=byte_flip——原 COMPLETE 33/33（五类全 Masked）全部不得作为 L03-F0 科学结果，也不得改标签转归其他模型；SEM-B 接线修复后须重走完整准入（config.ini 确认 l03 传入→count-only&gt;0→正/负对照→n=5→pilot→确定性重放→golden 回归）再重跑；数值列留空</t>
+        </is>
+      </c>
       <c r="AB286" s="39"/>
       <c r="AC286" s="39"/>
       <c r="AD286" s="39"/>
@@ -37119,10 +38061,16 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="Z288" s="35" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA288" s="34"/>
+      <c r="Z288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">进行中(准入s0完成)</t>
+        </is>
+      </c>
+      <c r="AA288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">W1 重跑前置进行中：准入 s0 PASS（i287_s0：chaos_lsqfwd l03Mode=true 实证、checkViolations_L03 站点 12,843 次真实 violation_addr_bitflip 注入、masked 全程跑完）；pilot-30 未启动，数值列留空；旧 300/0（短流事件不足 + --lsqfwd_l03 未接线）原样归档 runs/lsu/pilot/Load_Queue/ 不回填</t>
+        </is>
+      </c>
       <c r="AB288" s="39"/>
       <c r="AC288" s="39"/>
       <c r="AD288" s="39"/>
@@ -37307,10 +38255,16 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="Z290" s="35" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA290" s="34"/>
+      <c r="Z290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已阻塞(capability-gap)</t>
+        </is>
+      </c>
+      <c r="AA290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">capability-gap（D-2026-10-10-ITEM289）：CHAOSLSQFwd 无 F6 消费者注册（F-047(a) 三源审计，onF6Event 不可达）+ --lsqfwd_l03 未接线双重缺口；且 L03 清单触发语义（内存序违规）不在 4 种 F6 事件源内；SEM-F6 MemoryOrderViolation 事件源待实施（F-048 设计稿）并通过全部准入门后单独重跑，不得用 SqForward 近似映射生成结果；旧 300/0 已归档</t>
+        </is>
+      </c>
       <c r="AB290" s="39"/>
       <c r="AC290" s="39"/>
       <c r="AD290" s="39"/>
@@ -40862,7 +41816,7 @@
     <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="待执行"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="whole" sqref="Q2:W338 AB2:AJ338" xr:uid="{00000000-0002-0000-0700-000000000000}">
+    <dataValidation type="whole" sqref="Q2:W338 AB2:AJ338" ns2:uid="{00000000-0002-0000-0700-000000000000}">
       <formula1>0</formula1>
       <formula2>1000000000</formula2>
     </dataValidation>
